--- a/docs/pracovný denník.xlsx
+++ b/docs/pracovný denník.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="78">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -55,66 +55,129 @@
     <t xml:space="preserve">Literatúra [3] - ASR postupy (poznámky a časti do citácie)</t>
   </si>
   <si>
+    <t xml:space="preserve">Testovaný model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Počet testov</t>
+  </si>
+  <si>
     <t xml:space="preserve">Literatúra [4] - Technológie modelov STT (poznámky a časti do citácie)</t>
   </si>
   <si>
+    <t xml:space="preserve">faster_whisper_large_float16_cuda</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.1.2025</t>
   </si>
   <si>
     <t xml:space="preserve">Rozdelenie diplomovej práce na teoretickú a praktickú časť, predpripraviť kapitoly a podkapitoly</t>
   </si>
   <si>
+    <t xml:space="preserve">faster_whisper_medium_float16_cuda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3x 15.000</t>
+  </si>
+  <si>
     <t xml:space="preserve">Inštalácia Whisper OpenAI</t>
   </si>
   <si>
+    <t xml:space="preserve">huggingface_wav2vec2_xls_r_300m_czech</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.2.2025</t>
   </si>
   <si>
     <t xml:space="preserve">Inštalácia Python SpeechRecognition</t>
   </si>
   <si>
+    <t xml:space="preserve">huggingface_wav2vec2_xlsr_53_czech</t>
+  </si>
+  <si>
     <t xml:space="preserve">Inštalácia Wav2vec</t>
   </si>
   <si>
+    <t xml:space="preserve">huggingface_wav2vec2_xlsr_czech</t>
+  </si>
+  <si>
     <t xml:space="preserve">28.2.2025</t>
   </si>
   <si>
     <t xml:space="preserve">Python module pre Whisper</t>
   </si>
   <si>
+    <t xml:space="preserve">huggingface_wav2vec2_xlsr_czech_sammy</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python module pre Python SpeechRecognition (podpora 10 modelov)</t>
   </si>
   <si>
+    <t xml:space="preserve">huggingface_whisper_large_v3_czech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x 15.000</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python module pre Wav2vec (pridať podporu ďalších modelov vo Wav2vec)</t>
   </si>
   <si>
+    <t xml:space="preserve">whisper_large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3x 3.000</t>
+  </si>
+  <si>
     <t xml:space="preserve">Main Python testing script + JSON output</t>
   </si>
   <si>
+    <t xml:space="preserve">whisper_medium</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rozdelenie citácií do podkapitol teoretickej časti DP</t>
   </si>
   <si>
+    <t xml:space="preserve">whisper_small</t>
+  </si>
+  <si>
     <t xml:space="preserve">Diplomová práca do aktuálnej šablóny</t>
   </si>
   <si>
+    <t xml:space="preserve">whisper_tiny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5x 15.000</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.3.2025</t>
   </si>
   <si>
     <t xml:space="preserve">Koncept praktickej časti do kapitol DP</t>
   </si>
   <si>
+    <t xml:space="preserve">whisper_base</t>
+  </si>
+  <si>
     <t xml:space="preserve">Výber testovacieho materiálu (Common voice)</t>
   </si>
   <si>
+    <t xml:space="preserve">speech_recognition_google</t>
+  </si>
+  <si>
     <t xml:space="preserve">29.3.2025</t>
   </si>
   <si>
     <t xml:space="preserve">Filtrovanie validated materiálu</t>
   </si>
   <si>
+    <t xml:space="preserve">speech_recognition_groq</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python script na vytváranie kontrolného JSON file</t>
   </si>
   <si>
+    <t xml:space="preserve">speech_recognition_vosk</t>
+  </si>
+  <si>
     <t xml:space="preserve">30.3.2025</t>
   </si>
   <si>
@@ -154,25 +217,37 @@
     <t xml:space="preserve">27</t>
   </si>
   <si>
+    <t xml:space="preserve">25.3.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rework testovacieho frameworku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4.2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Príprava datasetov</t>
   </si>
   <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ošetrenie datasetov</t>
   </si>
   <si>
+    <t xml:space="preserve">15.4.2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Príprava CZ modelov</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rework testovacieho frameworku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rework teoretickej časti (popis testovania)</t>
+    <t xml:space="preserve">Rework praktickej časti (popis testovania)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testy na dlhších datasetoch</t>
   </si>
   <si>
     <t xml:space="preserve">Zmeny a aktuálny stav Diplomovej práce dostupný na:</t>
@@ -189,7 +264,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,6 +288,14 @@
       <family val="0"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
       <u val="single"/>
       <sz val="11"/>
       <color theme="10"/>
@@ -221,12 +304,30 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FAF46"/>
+        <bgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="15">
@@ -360,100 +461,140 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -543,12 +684,12 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF70AD47"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF3FAF46"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -737,7 +878,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.57"/>
@@ -746,7 +887,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="14"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="58"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="4" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="12.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="4" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -804,6 +946,12 @@
       <c r="D4" s="16" t="s">
         <v>6</v>
       </c>
+      <c r="F4" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="n">
@@ -813,10 +961,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -824,13 +978,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -838,13 +998,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -852,13 +1018,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -866,13 +1038,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -880,13 +1058,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="20" t="s">
         <v>18</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -894,13 +1078,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -908,13 +1098,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -922,13 +1118,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="20" t="s">
         <v>18</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -936,13 +1138,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="20" t="s">
         <v>18</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -950,13 +1158,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -964,13 +1178,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -978,13 +1198,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -992,13 +1218,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1006,13 +1238,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>6</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1020,14 +1258,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>6</v>
       </c>
+      <c r="G20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="n">
@@ -1035,25 +1274,28 @@
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="15" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>34</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F21" s="0"/>
+      <c r="G21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>6</v>
       </c>
+      <c r="G22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="n">
@@ -1061,11 +1303,13 @@
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="15" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>34</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="n">
@@ -1073,124 +1317,154 @@
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="15" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="n">
+      <c r="A25" s="23" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="15" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="n">
+      <c r="A26" s="23" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D26" s="16" t="s">
         <v>6</v>
       </c>
+      <c r="G26" s="0"/>
+      <c r="H26" s="0"/>
+      <c r="I26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>34</v>
-      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="0"/>
+      <c r="H27" s="0"/>
+      <c r="I27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="14"/>
+        <v>64</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>65</v>
+      </c>
       <c r="C28" s="15" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>34</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G28" s="0"/>
+      <c r="H28" s="0"/>
+      <c r="I28" s="0"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="14"/>
+        <v>67</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>68</v>
+      </c>
       <c r="C29" s="15" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>34</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G29" s="0"/>
+      <c r="H29" s="0"/>
+      <c r="I29" s="0"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="n">
+      <c r="A30" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="0" t="s">
-        <v>47</v>
+      <c r="B30" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>70</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="n">
+      <c r="A31" s="23" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="24" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>38</v>
+      <c r="B32" s="25"/>
+      <c r="C32" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="30"/>
+      <c r="C33" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="31" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C44" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="22" t="s">
-        <v>52</v>
+      <c r="C45" s="32" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1048576">
+  <conditionalFormatting sqref="D42:D1048576 D1:D28 D33:D37 C42:C43 C37">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Rework"</formula>
     </cfRule>
@@ -1201,6 +1475,34 @@
       <formula>"In progress"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>"Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C38:D41">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"Rework"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"To do"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>"In progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>"Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D32">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"Rework"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"To do"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>"In progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
